--- a/outputs/design_sweep/details/recommended_verified/details/params.xlsx
+++ b/outputs/design_sweep/details/recommended_verified/details/params.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>180</v>
+        <v>228.0186146497709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>235.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>228.0186146497709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>390</v>
+        <v>375.5000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250</v>
+        <v>343.9000000000001</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>180</v>
+        <v>228.0186146497709</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>390</v>
+        <v>375.5000000000001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>640</v>
+        <v>719.4000000000002</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>180</v>
+        <v>228.0186146497709</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>640</v>
+        <v>719.4000000000002</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>780</v>
+        <v>859.4000000000002</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>780</v>
+        <v>859.4000000000002</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>180</v>
+        <v>228.0186146497709</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -807,11 +807,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wing_span</t>
+          <t>fuselage_width</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3374.2</v>
+        <v>135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -827,11 +827,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wing_half_span</t>
+          <t>fuselage_height</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1687.1</v>
+        <v>228.0186146497709</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -847,15 +847,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wing_root_chord</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>325.8</v>
+          <t>fuselage_cross_section</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rectangular_filleted</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -867,11 +869,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>wing_tip_chord</t>
+          <t>fuselage_fillet_radius</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>195.48</v>
+        <v>20</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -887,11 +889,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wing_mac</t>
+          <t>wing_span</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>266.0699999999999</v>
+        <v>3374.2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -907,11 +909,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>wing_le_x</t>
+          <t>wing_half_span</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>323.4825</v>
+        <v>1687.1</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -927,11 +929,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>wing_ac_x</t>
+          <t>wing_root_chord</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>390</v>
+        <v>325.8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -947,15 +949,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>wing_taper_ratio</t>
+          <t>wing_tip_chord</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6</v>
+        <v>195.48</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -967,15 +969,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>wing_sweep</t>
+          <t>wing_mac</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>266.0699999999999</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -987,15 +989,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>wing_dihedral</t>
+          <t>wing_le_x</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>338.4825</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1007,15 +1009,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>wing_twist_root</t>
+          <t>wing_ac_x</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>404.9999999999999</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1027,15 +1029,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>wing_twist_tip</t>
+          <t>wing_z</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2</v>
+        <v>96.86430732488546</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1047,17 +1049,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>wing_NACA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NACA4412</t>
-        </is>
+          <t>wing_thickness</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>28</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1069,15 +1069,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>wing_primary_spar_OD</t>
+          <t>wing_taper_ratio</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.75000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1089,15 +1089,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>wing_primary_spar_ID</t>
+          <t>wing_sweep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.06250000000001</v>
+        <v>0</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1109,15 +1109,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>wing_primary_spar_chord_fraction</t>
+          <t>wing_dihedral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1129,15 +1129,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>wing_secondary_spar_chord_fraction</t>
+          <t>wing_twist_root</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1149,15 +1149,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>wing_secondary_spar_OD</t>
+          <t>wing_twist_tip</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1169,15 +1169,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>horizontal_tail_span</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>868.8000000000001</v>
+          <t>wing_NACA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NACA4412</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1189,11 +1191,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>horizontal_tail_half_span</t>
+          <t>wing_primary_spar_OD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>434.4</v>
+        <v>22.75000000000001</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1209,11 +1211,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>horizontal_tail_root_chord</t>
+          <t>wing_primary_spar_ID</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>218</v>
+        <v>17.06250000000001</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1229,15 +1231,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>horizontal_tail_tip_chord</t>
+          <t>wing_primary_spar_chord_fraction</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>152.6</v>
+        <v>0.25</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1249,15 +1251,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>horizontal_tail_mac</t>
+          <t>wing_secondary_spar_chord_fraction</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>187.2235294117647</v>
+        <v>0.65</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1269,11 +1271,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>horizontal_tail_le_x</t>
+          <t>wing_secondary_spar_OD</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1002.135900500583</v>
+        <v>10</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1289,11 +1291,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>horizontal_tail_ac_x</t>
+          <t>fuselage_longeron_OD</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1048.941782853524</v>
+        <v>6.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1309,15 +1311,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>horizontal_tail_taper_ratio</t>
+          <t>fuselage_longeron_boss_OD</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7</v>
+        <v>12.5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1329,17 +1331,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>horizontal_tail_NACA</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NACA0012</t>
-        </is>
+          <t>fuselage_longeron_top_z</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>110.7593073248855</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1351,11 +1351,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>horizontal_tail_primary_spar_OD</t>
+          <t>fuselage_longeron_bottom_z</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>9.500000000000005</v>
+        <v>-110.7593073248855</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1371,11 +1371,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>horizontal_tail_primary_spar_ID</t>
+          <t>fuselage_top_z</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7.125000000000004</v>
+        <v>114.0093073248855</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1391,11 +1391,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>horizontal_tail_secondary_spar_OD</t>
+          <t>wing_drop_from_flush</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>3.145000000000009</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1411,15 +1411,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>vertical_tail_count</t>
+          <t>horizontal_tail_span</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>868.8000000000001</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1431,11 +1431,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vertical_tail_height</t>
+          <t>horizontal_tail_half_span</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>300</v>
+        <v>434.4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1451,11 +1451,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vertical_tail_root_chord</t>
+          <t>horizontal_tail_root_chord</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1471,11 +1471,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vertical_tail_tip_chord</t>
+          <t>horizontal_tail_tip_chord</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>88.79999999999998</v>
+        <v>152.6</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1491,11 +1491,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vertical_tail_le_x</t>
+          <t>horizontal_tail_mac</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>991.3755147805939</v>
+        <v>187.2235294117647</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1511,11 +1511,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vertical_tail_ac_x</t>
+          <t>horizontal_tail_le_x</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1021.592181447261</v>
+        <v>962.6143656121251</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1531,15 +1531,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vertical_tail_taper_ratio</t>
+          <t>horizontal_tail_ac_x</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6</v>
+        <v>1009.420247965066</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1551,17 +1551,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vertical_tail_NACA</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NACA0012</t>
-        </is>
+          <t>horizontal_tail_z</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>96.86430732488546</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1573,11 +1571,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>vertical_tail_primary_spar_OD</t>
+          <t>horizontal_tail_thickness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>7.250000000000003</v>
+        <v>22</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1593,15 +1591,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vertical_tail_primary_spar_ID</t>
+          <t>horizontal_tail_taper_ratio</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5.437500000000003</v>
+        <v>0.7</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1613,15 +1611,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vertical_tail_secondary_spar_OD</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>4</v>
+          <t>horizontal_tail_NACA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NACA0012</t>
+        </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1633,11 +1633,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>boom_length</t>
+          <t>horizontal_tail_primary_spar_OD</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>760</v>
+        <v>9.500000000000005</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>boom_start_x</t>
+          <t>horizontal_tail_primary_spar_ID</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>340</v>
+        <v>7.125000000000004</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1673,11 +1673,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>boom_end_x</t>
+          <t>horizontal_tail_secondary_spar_OD</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1100</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1693,15 +1693,15 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>boom_left_y</t>
+          <t>vertical_tail_count</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-350</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1713,11 +1713,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>boom_right_y</t>
+          <t>vertical_tail_height</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1733,11 +1733,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>boom_spacing</t>
+          <t>vertical_tail_root_chord</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>700</v>
+        <v>148</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1753,11 +1753,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>boom_OD</t>
+          <t>vertical_tail_tip_chord</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>21.25000000000001</v>
+        <v>88.79999999999998</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1773,11 +1773,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>boom_ID</t>
+          <t>vertical_tail_le_x</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>17.25000000000001</v>
+        <v>969.7833333333333</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1793,11 +1793,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>lift_motor_front_x</t>
+          <t>vertical_tail_ac_x</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>96.48448753971806</v>
+        <v>1000</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1813,11 +1813,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>lift_motor_rear_x</t>
+          <t>vertical_tail_thickness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>675.284487539718</v>
+        <v>12</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1833,15 +1833,15 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lift_motor_y_abs</t>
+          <t>vertical_tail_taper_ratio</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>480</v>
+        <v>0.6</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1853,15 +1853,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>lift_motor_z</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>100</v>
+          <t>vertical_tail_NACA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NACA0012</t>
+        </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -1873,11 +1875,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>lift_prop_diameter</t>
+          <t>vertical_tail_primary_spar_OD</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>558.8</v>
+        <v>7.250000000000003</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1893,11 +1895,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>lift_prop_pitch</t>
+          <t>vertical_tail_primary_spar_ID</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>167.64</v>
+        <v>5.437500000000003</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1913,17 +1915,15 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>lift_motor_name</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Tmotor_U8Lite_150kV_P22x6p6_12S</t>
-        </is>
+          <t>vertical_tail_secondary_spar_OD</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1935,11 +1935,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lift_motor_OD</t>
+          <t>boom_length</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>87.09999999999999</v>
+        <v>1003.516</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -1955,11 +1955,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lift_motor_body_length</t>
+          <t>boom_start_x</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>27.05</v>
+        <v>96.48400000000001</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -1975,11 +1975,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>pusher_motor_x</t>
+          <t>boom_end_x</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>940</v>
+        <v>1100</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -1995,11 +1995,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>pusher_motor_y</t>
+          <t>boom_left_y</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>-366.9</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2015,11 +2015,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pusher_motor_z</t>
+          <t>boom_right_y</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>20</v>
+        <v>366.9</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2035,11 +2035,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>pusher_prop_diameter</t>
+          <t>boom_spacing</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>381</v>
+        <v>733.8</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2055,11 +2055,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>pusher_prop_pitch</t>
+          <t>boom_z</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>127</v>
+        <v>96.86430732488546</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2075,17 +2075,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>pusher_motor_name</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Tmotor_MN501S_240kV_P15x5_12S</t>
-        </is>
+          <t>boom_OD</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>21.25000000000001</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2097,11 +2095,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>pusher_motor_OD</t>
+          <t>boom_ID</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>55.59999999999999</v>
+        <v>17.25000000000001</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2117,11 +2115,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>pusher_motor_body_length</t>
+          <t>lift_motor_front_x</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>33.9</v>
+        <v>120.6378265749097</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2137,11 +2135,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>battery_x</t>
+          <t>lift_motor_rear_x</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>330.2874994984061</v>
+        <v>699.4378265749098</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2157,11 +2155,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>battery_y</t>
+          <t>lift_motor_y_abs</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>366.9</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2177,11 +2175,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>battery_z</t>
+          <t>lift_motor_z</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>63.1</v>
+        <v>127.8893073248855</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2197,11 +2195,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>battery_length</t>
+          <t>lift_prop_diameter</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>163</v>
+        <v>558.8</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2217,11 +2215,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>battery_width</t>
+          <t>lift_prop_pitch</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>92</v>
+        <v>167.64</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2237,15 +2235,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>battery_height</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>51</v>
+          <t>lift_motor_name</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tmotor_U8Lite_150kV_P22x6p6_12S</t>
+        </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2257,11 +2257,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>fuel_cell_x</t>
+          <t>lift_motor_OD</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>152.849637581354</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2277,11 +2277,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fuel_cell_y</t>
+          <t>lift_motor_body_length</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2297,11 +2297,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>fuel_cell_z</t>
+          <t>pusher_motor_x</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-25.465</v>
+        <v>896.3500000000003</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2317,11 +2317,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>fuel_cell_length</t>
+          <t>pusher_motor_y</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2337,11 +2337,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>fuel_cell_width</t>
+          <t>pusher_motor_z</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2357,11 +2357,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>fuel_cell_height</t>
+          <t>pusher_prop_diameter</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>120</v>
+        <v>381</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2377,11 +2377,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>hydrogen_cylinder_x</t>
+          <t>pusher_prop_pitch</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>526.501761579615</v>
+        <v>127</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2397,15 +2397,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>hydrogen_cylinder_y</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>0</v>
+          <t>pusher_motor_name</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Tmotor_MN501S_240kV_P15x5_12S</t>
+        </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2417,11 +2419,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>hydrogen_cylinder_z</t>
+          <t>pusher_motor_OD</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-28.28</v>
+        <v>55.59999999999999</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2437,11 +2439,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>hydrogen_cylinder_length</t>
+          <t>pusher_motor_body_length</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>450</v>
+        <v>33.9</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2457,11 +2459,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>hydrogen_cylinder_diameter</t>
+          <t>payload_x</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>120</v>
+        <v>103.5</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2477,11 +2479,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>general_print_tolerance</t>
+          <t>payload_y</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2490,18 +2492,18 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>User CAD tolerance/clearance</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>transition_fit_clearance</t>
+          <t>payload_z</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.24</v>
+        <v>-28.00930732488547</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2510,18 +2512,18 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>User CAD tolerance/clearance</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>carbon_tube_fit_clearance</t>
+          <t>payload_length</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5</v>
+        <v>53</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2530,18 +2532,18 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>User CAD tolerance/clearance</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>component_keepout_clearance</t>
+          <t>payload_width</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2550,18 +2552,18 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>User CAD tolerance/clearance</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>prop_disk_edge_clearance</t>
+          <t>payload_height</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2570,18 +2572,18 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>User CAD tolerance/clearance</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>bolt_pocket_diameter_clearance</t>
+          <t>battery_x</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.7</v>
+        <v>221.5</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2590,40 +2592,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>User CAD tolerance/clearance</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>default_motor_mount_fastener</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
+          <t>battery_y</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>bolt_M3_OD</t>
+          <t>battery_z</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>60.29069267511453</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2632,18 +2632,18 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bolt_M3_clearance_hole_OD</t>
+          <t>battery_length</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3.2</v>
+        <v>163</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2652,18 +2652,18 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bolt_M3_head_OD</t>
+          <t>battery_width</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>6.5</v>
+        <v>92</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -2672,18 +2672,18 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bolt_M4_OD</t>
+          <t>battery_height</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -2692,18 +2692,18 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bolt_M4_clearance_hole_OD</t>
+          <t>fuel_cell_x</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>4.2</v>
+        <v>255.25</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -2712,18 +2712,18 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bolt_M4_head_OD</t>
+          <t>fuel_cell_y</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8.220000000000001</v>
+        <v>0</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -2732,18 +2732,18 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bolt_M5_OD</t>
+          <t>fuel_cell_z</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>5</v>
+        <v>-28.10930732488547</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2752,18 +2752,18 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>bolt_M5_clearance_hole_OD</t>
+          <t>fuel_cell_length</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>5.2</v>
+        <v>230.5</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2772,18 +2772,18 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>bolt_M5_head_OD</t>
+          <t>fuel_cell_width</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>9.720000000000001</v>
+        <v>108.4</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2792,22 +2792,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>User CAD fastener parameter</t>
+          <t>H2AIR CAD export</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>wing_rib_count</t>
+          <t>fuel_cell_height</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15</v>
+        <v>119.8</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -2819,15 +2819,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>horizontal_tail_rib_count</t>
+          <t>fuel_cell_control_box_x</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>7</v>
+        <v>414.1</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -2839,18 +2839,940 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>fuel_cell_control_box_y</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>fuel_cell_control_box_z</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>57.36569267511453</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>fuel_cell_control_box_length</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>fuel_cell_control_box_width</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>107</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>fuel_cell_control_box_height</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>45.15000000000001</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>hydrogen_cylinder_x</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>593.0000000000001</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>hydrogen_cylinder_y</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>hydrogen_cylinder_z</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>-30.50930732488547</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>hydrogen_cylinder_length</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>425</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>hydrogen_cylinder_diameter</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>115</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cube_orange_x</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cube_orange_y</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cube_orange_z</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>30.49069267511453</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cube_orange_length</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cube_orange_width</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cube_orange_height</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>31</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>pdb_x</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>565.2</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>pdb_y</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>pdb_z</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>63.54069267511453</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>pdb_length</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>80</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>pdb_width</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>60</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>pdb_height</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>pdb2_x</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>655.2000000000002</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>pdb2_y</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>pdb2_z</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>63.54069267511453</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>pdb2_length</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>80</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>pdb2_width</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>60</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>pdb2_height</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>general_print_tolerance</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>User CAD tolerance/clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>transition_fit_clearance</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>User CAD tolerance/clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>carbon_tube_fit_clearance</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>User CAD tolerance/clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>component_keepout_clearance</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>User CAD tolerance/clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>prop_disk_edge_clearance</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>20</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>User CAD tolerance/clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>bolt_pocket_diameter_clearance</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>User CAD tolerance/clearance</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>default_motor_mount_fastener</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>bolt_M3_OD</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>bolt_M3_clearance_hole_OD</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>bolt_M3_head_OD</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>bolt_M4_OD</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>bolt_M4_clearance_hole_OD</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>bolt_M4_head_OD</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>bolt_M5_OD</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>bolt_M5_clearance_hole_OD</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>bolt_M5_head_OD</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>User CAD fastener parameter</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>wing_rib_count</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>15</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>horizontal_tail_rib_count</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>7</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>H2AIR CAD export</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
           <t>vertical_tail_rib_count_each</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B167" t="n">
         <v>4</v>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C167" t="inlineStr">
         <is>
           <t>unitless</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>H2AIR CAD export</t>
         </is>
